--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105352_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105352_W2.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.863</v>
+        <v>4.7468</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1501</v>
+        <v>3.0647</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7129</v>
+        <v>1.6821</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9891</v>
+        <v>1.8267</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2919</v>
+        <v>2.2307</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3029</v>
+        <v>-0.404</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4328</v>
+        <v>2.4888</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1374</v>
+        <v>2.1924</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2954</v>
+        <v>0.2964</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4437</v>
+        <v>-0.6621</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1545</v>
+        <v>0.0383</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.7004</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R2" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0816</v>
+        <v>1.1266</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4171</v>
+        <v>1.2609</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3355</v>
+        <v>-0.1343</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2538</v>
+        <v>2.2524</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5691</v>
+        <v>1.5606</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4701</v>
+        <v>2.4407</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8841</v>
+        <v>1.8732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5859</v>
+        <v>0.5676</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5472</v>
+        <v>1.5564</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6272</v>
+        <v>-0.6397</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1743</v>
+        <v>2.1961</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2482</v>
+        <v>1.3242</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7906</v>
+        <v>-0.7573</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0388</v>
+        <v>2.0815</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2989</v>
+        <v>0.2322</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1634</v>
+        <v>0.1176</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1355</v>
+        <v>0.1146</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.5894</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6359</v>
+        <v>0.549</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0205</v>
+        <v>0.0404</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,64 +736,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5951</v>
+        <v>0.5355</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1716</v>
+        <v>-0.1903</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7667</v>
+        <v>0.7258</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.8231</v>
+        <v>-2.7789</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3172</v>
+        <v>-1.3035</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.506</v>
+        <v>-1.4754</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.9085</v>
+        <v>-1.8056</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2997</v>
+        <v>-0.2628</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.6088</v>
+        <v>-1.5428</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9146</v>
+        <v>-0.9732</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0174</v>
+        <v>-1.0407</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1028</v>
+        <v>0.0674</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S4" t="n">
-        <v>0.726</v>
+        <v>0.6259</v>
       </c>
       <c r="T4" t="n">
-        <v>0.66</v>
+        <v>0.5333</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0926</v>
       </c>
       <c r="V4" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="W4" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0751</v>
+        <v>0.0804</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3835</v>
+        <v>2.4416</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3083</v>
+        <v>-2.3612</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8434</v>
+        <v>0.8818</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0508</v>
+        <v>-0.0512</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8941</v>
+        <v>0.9329</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0167</v>
+        <v>1.2055</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.041</v>
+        <v>0.037</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0577</v>
+        <v>1.1685</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1734</v>
+        <v>-0.3238</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0881</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1636</v>
+        <v>-0.2356</v>
       </c>
       <c r="P5" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4627</v>
+        <v>0.4446</v>
       </c>
       <c r="T5" t="n">
-        <v>1.059</v>
+        <v>0.9245</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5962</v>
+        <v>-0.4799</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.6925</v>
+        <v>-2.705</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,64 +902,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2603</v>
+        <v>-0.1847</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8601</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5998</v>
+        <v>0.5608</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.912</v>
+        <v>-1.8256</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9927</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9194</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2031</v>
+        <v>-0.9872</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1531</v>
+        <v>-1.0443</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.05</v>
+        <v>0.057</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7089</v>
+        <v>-0.8383</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1604</v>
+        <v>0.0912</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8694</v>
+        <v>-0.9295</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1285</v>
+        <v>1.1097</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2044</v>
+        <v>1.0875</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.07580000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2924</v>
+        <v>0.3017</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2924</v>
+        <v>0.3017</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5431</v>
+        <v>-2.5194</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5495</v>
+        <v>-3.4906</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0064</v>
+        <v>0.9712</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.4485</v>
+        <v>-3.3791</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6292</v>
+        <v>-0.6573</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8194</v>
+        <v>-2.7218</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.2407</v>
+        <v>-3.1085</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0508</v>
+        <v>0.0512</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.2914</v>
+        <v>-3.1597</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2078</v>
+        <v>-0.2705</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.7085</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4721</v>
+        <v>0.4379</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1021</v>
+        <v>-0.1369</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3088</v>
+        <v>-0.3821</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2067</v>
+        <v>0.2451</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,67 +1068,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0191</v>
+        <v>-2.9923</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3403</v>
+        <v>-2.264</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6788</v>
+        <v>-0.7284</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.78</v>
+        <v>-0.7276</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7194</v>
+        <v>-1.6774</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9395</v>
+        <v>0.9498</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4403</v>
+        <v>-0.2598</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7116</v>
+        <v>-1.6069</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2713</v>
+        <v>1.3471</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3397</v>
+        <v>-0.4678</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0078</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3318</v>
+        <v>-0.3973</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.846</v>
+        <v>-1.836</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5383</v>
+        <v>-2.5244</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6839</v>
+        <v>0.6533</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6383</v>
+        <v>0.5203</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0456</v>
+        <v>0.133</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1189</v>
+        <v>-3.1012</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3781</v>
+        <v>-3.3095</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2592</v>
+        <v>0.2082</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3854</v>
+        <v>-0.3602</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0199</v>
+        <v>-0.0435</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3655</v>
+        <v>-0.3167</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6159</v>
+        <v>-0.4717</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.012</v>
+        <v>0.027</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6039</v>
+        <v>-0.4987</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2305</v>
+        <v>0.1115</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0078</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2384</v>
+        <v>0.182</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7691</v>
+        <v>-2.7539</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6921</v>
+        <v>-3.6719</v>
       </c>
       <c r="R9" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9663</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7837</v>
+        <v>0.6833</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1826</v>
+        <v>0.2608</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9308</v>
+        <v>-0.9312</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3941</v>
+        <v>-3.3472</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1072</v>
+        <v>-1.9985</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2869</v>
+        <v>-1.3487</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5016</v>
+        <v>-2.4582</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.481</v>
+        <v>-2.4447</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0206</v>
+        <v>-0.0135</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7878</v>
+        <v>-1.5758</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.627</v>
+        <v>-1.5217</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1608</v>
+        <v>-0.0541</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7138</v>
+        <v>-0.8824</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8541</v>
+        <v>-0.923</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1402</v>
+        <v>0.0406</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6923</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5925</v>
+        <v>-0.5907</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0119</v>
+        <v>-0.1278</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5806</v>
+        <v>-0.4629</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3923</v>
+        <v>0.3901</v>
       </c>
       <c r="W10" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9084</v>
+        <v>-3.8815</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5998</v>
+        <v>-2.5325</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3086</v>
+        <v>-1.349</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9605</v>
+        <v>-2.9329</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2767</v>
+        <v>-0.3257</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6838</v>
+        <v>-2.6072</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2698</v>
+        <v>-1.1275</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9139</v>
+        <v>0.9207</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1837</v>
+        <v>-2.0482</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6907</v>
+        <v>-1.8054</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1906</v>
+        <v>-1.2464</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5001</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7019</v>
+        <v>-0.7093</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0698</v>
+        <v>-0.0183</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.6911</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2461</v>
+        <v>-0.2393</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2461</v>
+        <v>-0.2393</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,64 +1400,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2895</v>
+        <v>-7.1737</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.3712</v>
+        <v>-6.2319</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9183</v>
+        <v>-0.9418</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.439</v>
+        <v>-6.3681</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6353</v>
+        <v>-2.6158</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.8037</v>
+        <v>-3.7523</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.3107</v>
+        <v>-4.0715</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.61</v>
+        <v>-1.5046</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7007</v>
+        <v>-2.5669</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1283</v>
+        <v>-2.2966</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0253</v>
+        <v>-1.1112</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1031</v>
+        <v>-1.1854</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.846</v>
+        <v>-1.836</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4613</v>
+        <v>-3.4424</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3738</v>
+        <v>-0.3534</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0314</v>
+        <v>-0.1017</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4052</v>
+        <v>-0.2517</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3694</v>
+        <v>1.3838</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3694</v>
+        <v>1.3838</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.5301</v>
+        <v>-15.3966</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.9601</v>
+        <v>-13.3833</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.57</v>
+        <v>-2.0134</v>
       </c>
       <c r="G13" t="n">
-        <v>-16.8704</v>
+        <v>-16.5657</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.4575</v>
+        <v>-8.481200000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.413399999999999</v>
+        <v>-8.0846</v>
       </c>
       <c r="J13" t="n">
-        <v>-10.0791</v>
+        <v>-8.389100000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.1429</v>
+        <v>-3.4693</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.9361</v>
+        <v>-4.919899999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.791499999999999</v>
+        <v>-8.176399999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.314400000000001</v>
+        <v>-5.0118</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.4773</v>
+        <v>-3.1647</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3075</v>
+        <v>-2.294900000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.9991</v>
+        <v>-14.9172</v>
       </c>
       <c r="R13" t="n">
-        <v>12.6916</v>
+        <v>12.6225</v>
       </c>
       <c r="S13" t="n">
-        <v>3.894099999999999</v>
+        <v>3.7033</v>
       </c>
       <c r="T13" t="n">
-        <v>6.178899999999999</v>
+        <v>4.9289</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2845</v>
+        <v>-1.2258</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2462</v>
+        <v>-0.2394000000000003</v>
       </c>
       <c r="W13" t="n">
-        <v>4.9391</v>
+        <v>4.994</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.185300000000001</v>
+        <v>-5.2332</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1986</v>
+        <v>5.084</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6972</v>
+        <v>2.6144</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5014</v>
+        <v>2.4696</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2786</v>
+        <v>3.1594</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8514</v>
+        <v>2.8022</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4272</v>
+        <v>0.3572</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4048</v>
+        <v>2.4218</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1833</v>
+        <v>2.1995</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2215</v>
+        <v>0.2223</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8738</v>
+        <v>0.7376</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6682</v>
+        <v>0.6027</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2057</v>
+        <v>0.1349</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3075</v>
+        <v>2.295</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3075</v>
+        <v>2.295</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1046</v>
+        <v>0.1082</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6383</v>
+        <v>0.5203</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.412</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4921</v>
+        <v>-0.4785</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3459</v>
+        <v>-0.3277</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0693</v>
+        <v>4.0563</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1284</v>
+        <v>4.1385</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0592</v>
+        <v>-0.0822</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2978</v>
+        <v>3.2296</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7423</v>
+        <v>1.7474</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5555</v>
+        <v>1.4822</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7605</v>
+        <v>2.8154</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5789</v>
+        <v>1.6298</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1816</v>
+        <v>1.1856</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5373</v>
+        <v>0.4142</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1634</v>
+        <v>0.1176</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3739</v>
+        <v>0.2966</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0793</v>
+        <v>0.1382</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2475</v>
+        <v>-0.2999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3268</v>
+        <v>0.4381</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6155</v>
+        <v>1.623</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6155</v>
+        <v>-1.623</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2844</v>
+        <v>3.3005</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7387</v>
+        <v>0.796</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5457</v>
+        <v>2.5045</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6374</v>
+        <v>3.6116</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8239</v>
+        <v>1.8062</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8135</v>
+        <v>1.8054</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4886</v>
+        <v>1.6096</v>
       </c>
       <c r="K16" t="n">
-        <v>1.325</v>
+        <v>1.374</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1636</v>
+        <v>0.2356</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1488</v>
+        <v>2.002</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4989</v>
+        <v>0.4322</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6499</v>
+        <v>1.5698</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3316</v>
+        <v>0.3808</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4039</v>
+        <v>0.3338</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0722</v>
+        <v>0.0469</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2156</v>
+        <v>3.1374</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1991</v>
+        <v>1.1569</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0165</v>
+        <v>1.9805</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0715</v>
+        <v>0.9937</v>
       </c>
       <c r="H17" t="n">
-        <v>1.588</v>
+        <v>1.5763</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5165</v>
+        <v>-0.5826</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7699</v>
+        <v>0.8531</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4266</v>
+        <v>1.4763</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6567</v>
+        <v>-0.6232</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3016</v>
+        <v>0.1406</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1614</v>
+        <v>0.1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1402</v>
+        <v>0.0406</v>
       </c>
       <c r="P17" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S17" t="n">
-        <v>0.298</v>
+        <v>0.3077</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4292</v>
+        <v>0.3038</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1312</v>
+        <v>0.0039</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1894,64 +1894,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8495</v>
+        <v>2.9385</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4532</v>
+        <v>0.6086</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3963</v>
+        <v>2.3299</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4108</v>
+        <v>1.4953</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0753</v>
+        <v>-1.0207</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4861</v>
+        <v>2.516</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7726</v>
+        <v>1.0313</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0685</v>
+        <v>-0.959</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8411</v>
+        <v>1.9903</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6382</v>
+        <v>0.464</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0069</v>
+        <v>-0.0617</v>
       </c>
       <c r="O18" t="n">
-        <v>0.645</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R18" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3305</v>
+        <v>-0.3273</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2426</v>
+        <v>-0.3573</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="V18" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="W18" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4174</v>
+        <v>1.453</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.9401</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5883</v>
+        <v>0.5129</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3286</v>
+        <v>-0.278</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4062</v>
+        <v>0.4092</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7348</v>
+        <v>-0.6872</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3677</v>
+        <v>-1.1508</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0775</v>
+        <v>0.1564</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4452</v>
+        <v>-1.3072</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0391</v>
+        <v>0.8728</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3287</v>
+        <v>0.2529</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7105</v>
+        <v>0.6199</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1154</v>
+        <v>0.1147</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9736</v>
+        <v>0.858</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8582</v>
+        <v>-0.7433</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2461</v>
+        <v>0.2393</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9771</v>
+        <v>-0.9936</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3195</v>
+        <v>1.3342</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6508</v>
+        <v>0.7117</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6687</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6233</v>
+        <v>1.6061</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1533</v>
+        <v>-0.1623</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7766</v>
+        <v>1.7683</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2457</v>
+        <v>0.3923</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9887</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2344</v>
+        <v>1.3101</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3776</v>
+        <v>1.2138</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8354</v>
+        <v>0.7556</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5422</v>
+        <v>0.4583</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2344</v>
+        <v>-0.1865</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4051</v>
+        <v>0.3195</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6395</v>
+        <v>-0.5059</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,64 +2143,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6633</v>
+        <v>0.7067</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5002</v>
+        <v>-2.3822</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1635</v>
+        <v>3.0889</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1716</v>
+        <v>2.1829</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5735</v>
+        <v>2.6005</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.402</v>
+        <v>-0.4176</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2891</v>
+        <v>0.484</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0746</v>
+        <v>2.1683</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7855</v>
+        <v>-1.6843</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8824</v>
+        <v>1.6989</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4989</v>
+        <v>0.4322</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3835</v>
+        <v>1.2667</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6153</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4613</v>
+        <v>-3.4424</v>
       </c>
       <c r="R21" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4315</v>
+        <v>-0.4107</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1335</v>
+        <v>0.0352</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.446</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2226,64 +2226,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5284</v>
+        <v>-0.582</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5252</v>
+        <v>-3.5163</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9968</v>
+        <v>2.9344</v>
       </c>
       <c r="G22" t="n">
-        <v>3.059</v>
+        <v>2.9481</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9017</v>
+        <v>1.8297</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1573</v>
+        <v>1.1183</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5775</v>
+        <v>1.658</v>
       </c>
       <c r="K22" t="n">
-        <v>0.897</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6805</v>
+        <v>0.7543</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4814</v>
+        <v>1.2901</v>
       </c>
       <c r="N22" t="n">
-        <v>1.0047</v>
+        <v>0.9261</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4768</v>
+        <v>0.364</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.1536</v>
+        <v>-4.1309</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.7689</v>
+        <v>-5.7374</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5108</v>
+        <v>-0.4812</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4109</v>
+        <v>-0.519</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0999</v>
+        <v>0.0378</v>
       </c>
       <c r="V22" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="W22" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2309,40 +2309,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6366</v>
+        <v>-1.66</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2408</v>
+        <v>-1.2197</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3957</v>
+        <v>-0.4403</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4339</v>
+        <v>-1.4374</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6711</v>
+        <v>-0.6291</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7628</v>
+        <v>-0.8083</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6039</v>
+        <v>-1.4987</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8364</v>
+        <v>-0.7644</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7675</v>
+        <v>-0.7343</v>
       </c>
       <c r="M23" t="n">
-        <v>0.17</v>
+        <v>0.0613</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1653</v>
+        <v>0.1352</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0047</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0565</v>
+        <v>-0.0717</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3631</v>
+        <v>0.279</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4195</v>
+        <v>-0.3508</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7024</v>
+        <v>-1.7379</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8601</v>
+        <v>-1.8346</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1577</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9169</v>
+        <v>-0.9455</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.5299</v>
+        <v>-2.4782</v>
       </c>
       <c r="I24" t="n">
-        <v>1.613</v>
+        <v>1.5327</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5454</v>
+        <v>-0.4394</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.3547</v>
+        <v>-2.2548</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8093</v>
+        <v>1.8155</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3714</v>
+        <v>-0.5061</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1751</v>
+        <v>-0.2234</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1963</v>
+        <v>-0.2828</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6394</v>
+        <v>-0.6415</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1609</v>
+        <v>-0.2478</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4784</v>
+        <v>-0.3938</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.1502</v>
+        <v>18.0307</v>
       </c>
       <c r="E25" t="n">
-        <v>1.570200000000001</v>
+        <v>2.013399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>16.58</v>
+        <v>16.0174</v>
       </c>
       <c r="G25" t="n">
-        <v>16.8706</v>
+        <v>16.5658</v>
       </c>
       <c r="H25" t="n">
-        <v>8.457400000000002</v>
+        <v>8.481200000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>8.4131</v>
+        <v>8.084399999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>6.791700000000001</v>
+        <v>8.176600000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3146</v>
+        <v>5.012</v>
       </c>
       <c r="L25" t="n">
-        <v>2.4771</v>
+        <v>3.1647</v>
       </c>
       <c r="M25" t="n">
-        <v>10.0788</v>
+        <v>8.389200000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1429</v>
+        <v>3.4694</v>
       </c>
       <c r="O25" t="n">
-        <v>5.9361</v>
+        <v>4.9198</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3075</v>
+        <v>2.295100000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.6916</v>
+        <v>-12.6223</v>
       </c>
       <c r="R25" t="n">
-        <v>14.999</v>
+        <v>14.9175</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2742</v>
+        <v>-1.0693</v>
       </c>
       <c r="T25" t="n">
-        <v>2.284800000000001</v>
+        <v>1.2256</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.5588</v>
+        <v>-2.2951</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2461999999999998</v>
+        <v>0.2392000000000002</v>
       </c>
       <c r="W25" t="n">
-        <v>5.1853</v>
+        <v>5.2332</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.9391</v>
+        <v>-4.9941</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105352_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105352_W2.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7468</v>
+        <v>4.807</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0647</v>
+        <v>2.8685</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6821</v>
+        <v>1.9385</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8267</v>
+        <v>1.8392</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2307</v>
+        <v>2.2131</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.404</v>
+        <v>-0.3739</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4888</v>
+        <v>2.4072</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1924</v>
+        <v>2.1144</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2964</v>
+        <v>0.2928</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6621</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0383</v>
+        <v>0.0987</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7004</v>
+        <v>-0.6667</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R2" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1266</v>
+        <v>1.1783</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2609</v>
+        <v>1.1988</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1343</v>
+        <v>-0.0204</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2524</v>
+        <v>2.2574</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5606</v>
+        <v>1.591</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4407</v>
+        <v>2.4745</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8732</v>
+        <v>1.8004</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5676</v>
+        <v>0.6741</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5564</v>
+        <v>1.5471</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6397</v>
+        <v>-0.6188</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1961</v>
+        <v>2.1659</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3242</v>
+        <v>1.2894</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7573</v>
+        <v>-0.7579</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0815</v>
+        <v>2.0473</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2322</v>
+        <v>0.2577</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1176</v>
+        <v>0.1391</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1146</v>
+        <v>0.1186</v>
       </c>
       <c r="P3" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5894</v>
+        <v>0.5877</v>
       </c>
       <c r="T3" t="n">
-        <v>0.549</v>
+        <v>0.5109</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0404</v>
+        <v>0.0767</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,64 +736,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5355</v>
+        <v>0.5357</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1903</v>
+        <v>-0.2826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7258</v>
+        <v>0.8184</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.7789</v>
+        <v>-2.7481</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3035</v>
+        <v>-1.2816</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4754</v>
+        <v>-1.4665</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.8056</v>
+        <v>-1.8186</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2628</v>
+        <v>-0.2764</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5428</v>
+        <v>-1.5422</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9732</v>
+        <v>-0.9295</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0407</v>
+        <v>-1.0051</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0674</v>
+        <v>0.0756</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6259</v>
+        <v>0.5819</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5333</v>
+        <v>0.4718</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0926</v>
+        <v>0.1101</v>
       </c>
       <c r="V4" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W4" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0804</v>
+        <v>0.1147</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4416</v>
+        <v>2.2879</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3612</v>
+        <v>-2.1732</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8818</v>
+        <v>0.8628</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0512</v>
+        <v>-0.0498</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9329</v>
+        <v>0.9126</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2055</v>
+        <v>1.1225</v>
       </c>
       <c r="K5" t="n">
-        <v>0.037</v>
+        <v>-0.0049</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1685</v>
+        <v>1.1274</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3238</v>
+        <v>-0.2596</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0881</v>
+        <v>-0.0449</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2356</v>
+        <v>-0.2148</v>
       </c>
       <c r="P5" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4446</v>
+        <v>0.4442</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9245</v>
+        <v>0.8673</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4799</v>
+        <v>-0.4231</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="W5" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.705</v>
+        <v>-2.6603</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,64 +902,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1847</v>
+        <v>-0.2007</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.9059</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5608</v>
+        <v>0.7052</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8256</v>
+        <v>-1.8272</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.9526</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.8746</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9872</v>
+        <v>-1.049</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0443</v>
+        <v>-1.0783</v>
       </c>
       <c r="L6" t="n">
-        <v>0.057</v>
+        <v>0.0293</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8383</v>
+        <v>-0.7782</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0912</v>
+        <v>0.1256</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9295</v>
+        <v>-0.9039</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R6" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1097</v>
+        <v>1.1239</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0875</v>
+        <v>1.0443</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0222</v>
+        <v>0.0796</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3017</v>
+        <v>0.2686</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3017</v>
+        <v>0.2686</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5194</v>
+        <v>-2.4684</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4906</v>
+        <v>-3.5411</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9712</v>
+        <v>1.0727</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3791</v>
+        <v>-3.3437</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6573</v>
+        <v>-0.6278</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.7218</v>
+        <v>-2.7159</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.1085</v>
+        <v>-3.1078</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0512</v>
+        <v>0.0498</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.1597</v>
+        <v>-3.1576</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2705</v>
+        <v>-0.2359</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7085</v>
+        <v>-0.6776</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4379</v>
+        <v>0.4417</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1369</v>
+        <v>-0.1602</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3821</v>
+        <v>-0.4333</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2451</v>
+        <v>0.2731</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,67 +1068,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9923</v>
+        <v>-3.0111</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.264</v>
+        <v>-2.4235</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7284</v>
+        <v>-0.5876</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7276</v>
+        <v>-0.7255</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6774</v>
+        <v>-1.6621</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9498</v>
+        <v>0.9365</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2598</v>
+        <v>-0.3133</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6069</v>
+        <v>-1.6261</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3471</v>
+        <v>1.3128</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4678</v>
+        <v>-0.4122</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0359</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3973</v>
+        <v>-0.3763</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5244</v>
+        <v>-2.5737</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6533</v>
+        <v>0.6503</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5203</v>
+        <v>0.4635</v>
       </c>
       <c r="U8" t="n">
-        <v>0.133</v>
+        <v>0.1868</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1012</v>
+        <v>-3.1405</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3095</v>
+        <v>-3.4827</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2082</v>
+        <v>0.3422</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3602</v>
+        <v>-0.3556</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0435</v>
+        <v>-0.0301</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3167</v>
+        <v>-0.3255</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4717</v>
+        <v>-0.5139</v>
       </c>
       <c r="K9" t="n">
-        <v>0.027</v>
+        <v>0.0058</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4987</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1115</v>
+        <v>0.1583</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0359</v>
       </c>
       <c r="O9" t="n">
-        <v>0.182</v>
+        <v>0.1942</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7539</v>
+        <v>-2.8077</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6719</v>
+        <v>-3.7436</v>
       </c>
       <c r="R9" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9526</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6833</v>
+        <v>0.6404</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2608</v>
+        <v>0.3121</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9312</v>
+        <v>-0.9298</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3472</v>
+        <v>-3.3315</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9985</v>
+        <v>-2.1614</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3487</v>
+        <v>-1.1701</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4582</v>
+        <v>-2.4243</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4447</v>
+        <v>-2.4092</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0135</v>
+        <v>-0.0151</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5758</v>
+        <v>-1.6236</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5217</v>
+        <v>-1.5431</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0541</v>
+        <v>-0.0805</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8824</v>
+        <v>-0.8007</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.923</v>
+        <v>-0.8661</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0406</v>
+        <v>0.0654</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6885</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5907</v>
+        <v>-0.603</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1278</v>
+        <v>-0.198</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4629</v>
+        <v>-0.405</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3901</v>
+        <v>0.3978</v>
       </c>
       <c r="W10" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8815</v>
+        <v>-3.8831</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5325</v>
+        <v>-2.6661</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.349</v>
+        <v>-1.2171</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9329</v>
+        <v>-2.8899</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3257</v>
+        <v>-0.2926</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6072</v>
+        <v>-2.5973</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1275</v>
+        <v>-1.1629</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9207</v>
+        <v>0.8966</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0482</v>
+        <v>-2.0595</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8054</v>
+        <v>-1.727</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2464</v>
+        <v>-1.1891</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7093</v>
+        <v>-0.7298</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0183</v>
+        <v>-0.0698</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6911</v>
+        <v>-0.66</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2393</v>
+        <v>-0.2634</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2393</v>
+        <v>-0.2634</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,64 +1400,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1737</v>
+        <v>-7.1794</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2319</v>
+        <v>-6.4567</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9418</v>
+        <v>-0.7227</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.3681</v>
+        <v>-6.2908</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6158</v>
+        <v>-2.5676</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.7523</v>
+        <v>-3.7232</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.0715</v>
+        <v>-4.0985</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5046</v>
+        <v>-1.5265</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5669</v>
+        <v>-2.5719</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2966</v>
+        <v>-2.1924</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1112</v>
+        <v>-1.0411</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1854</v>
+        <v>-1.1513</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3534</v>
+        <v>-0.3495</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1017</v>
+        <v>-0.1814</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2517</v>
+        <v>-0.1682</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3838</v>
+        <v>1.3327</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3838</v>
+        <v>1.3327</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.3966</v>
+        <v>-15.2828</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.3833</v>
+        <v>-14.9632</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0134</v>
+        <v>-0.3195999999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>-16.5657</v>
+        <v>-16.356</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.481200000000001</v>
+        <v>-8.2791</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.0846</v>
+        <v>-8.077</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.389100000000001</v>
+        <v>-8.868500000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.4693</v>
+        <v>-3.7466</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.919899999999999</v>
+        <v>-5.1218</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.176399999999999</v>
+        <v>-7.487500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.0118</v>
+        <v>-4.5323</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.1647</v>
+        <v>-2.9553</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.294900000000001</v>
+        <v>-2.3397</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.9172</v>
+        <v>-15.2083</v>
       </c>
       <c r="R13" t="n">
-        <v>12.6225</v>
+        <v>12.8685</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7033</v>
+        <v>3.6764</v>
       </c>
       <c r="T13" t="n">
-        <v>4.9289</v>
+        <v>4.3145</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2258</v>
+        <v>-0.6383</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2394000000000003</v>
+        <v>-0.2633000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>4.994</v>
+        <v>4.7989</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.2332</v>
+        <v>-5.0623</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.084</v>
+        <v>5.062</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6144</v>
+        <v>2.4323</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4696</v>
+        <v>2.6297</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1594</v>
+        <v>3.1364</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8022</v>
+        <v>2.7655</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3572</v>
+        <v>0.3709</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4218</v>
+        <v>2.3614</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1995</v>
+        <v>2.1418</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2223</v>
+        <v>0.2196</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7376</v>
+        <v>0.775</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6027</v>
+        <v>0.6237</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1349</v>
+        <v>0.1513</v>
       </c>
       <c r="P14" t="n">
-        <v>2.295</v>
+        <v>2.3397</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.295</v>
+        <v>2.3397</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1082</v>
+        <v>0.1128</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5203</v>
+        <v>0.4635</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.412</v>
+        <v>-0.3507</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4785</v>
+        <v>-0.5269</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3277</v>
+        <v>-0.3926</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0563</v>
+        <v>4.0672</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1385</v>
+        <v>3.9968</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0822</v>
+        <v>0.0704</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2296</v>
+        <v>3.1897</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7474</v>
+        <v>1.7056</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4822</v>
+        <v>1.4841</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8154</v>
+        <v>2.7378</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6298</v>
+        <v>1.5665</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1856</v>
+        <v>1.1713</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4142</v>
+        <v>0.4519</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1176</v>
+        <v>0.1391</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2966</v>
+        <v>0.3128</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1382</v>
+        <v>0.1756</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2999</v>
+        <v>-0.3372</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4381</v>
+        <v>0.5128</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.623</v>
+        <v>1.5962</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3005</v>
+        <v>3.3139</v>
       </c>
       <c r="E16" t="n">
-        <v>0.796</v>
+        <v>0.663</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5045</v>
+        <v>2.6509</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6116</v>
+        <v>3.5623</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8062</v>
+        <v>1.7751</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8054</v>
+        <v>1.7872</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6096</v>
+        <v>1.5322</v>
       </c>
       <c r="K16" t="n">
-        <v>1.374</v>
+        <v>1.3175</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2356</v>
+        <v>0.2148</v>
       </c>
       <c r="M16" t="n">
-        <v>2.002</v>
+        <v>2.0301</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4322</v>
+        <v>0.4577</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5698</v>
+        <v>1.5724</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3808</v>
+        <v>0.4179</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3338</v>
+        <v>0.3007</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0469</v>
+        <v>0.1173</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1374</v>
+        <v>3.18</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1569</v>
+        <v>1.0303</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9805</v>
+        <v>2.1498</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9937</v>
+        <v>0.9879</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5763</v>
+        <v>1.5472</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5826</v>
+        <v>-0.5593</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8531</v>
+        <v>0.7924</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4763</v>
+        <v>1.4171</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6232</v>
+        <v>-0.6247</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1406</v>
+        <v>0.1955</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1</v>
+        <v>0.1301</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0406</v>
+        <v>0.0654</v>
       </c>
       <c r="P17" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3077</v>
+        <v>0.3203</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3038</v>
+        <v>0.2379</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0039</v>
+        <v>0.0825</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1894,64 +1894,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9385</v>
+        <v>2.8867</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6086</v>
+        <v>0.3972</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3299</v>
+        <v>2.4895</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4953</v>
+        <v>1.4535</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0207</v>
+        <v>-1.0267</v>
       </c>
       <c r="I18" t="n">
-        <v>2.516</v>
+        <v>2.4802</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0313</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.959</v>
+        <v>-0.9952</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9903</v>
+        <v>1.9302</v>
       </c>
       <c r="M18" t="n">
-        <v>0.464</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0617</v>
+        <v>-0.0314</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R18" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3273</v>
+        <v>-0.3328</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3573</v>
+        <v>-0.432</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03</v>
+        <v>0.0992</v>
       </c>
       <c r="V18" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W18" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.453</v>
+        <v>1.4912</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9401</v>
+        <v>0.7926</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5129</v>
+        <v>0.6986</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.278</v>
+        <v>-0.2931</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4092</v>
+        <v>0.3985</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6872</v>
+        <v>-0.6915</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1508</v>
+        <v>-1.2161</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1564</v>
+        <v>0.1113</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3072</v>
+        <v>-1.3274</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8728</v>
+        <v>0.9231</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2529</v>
+        <v>0.2872</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6199</v>
+        <v>0.6359</v>
       </c>
       <c r="P19" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1147</v>
+        <v>0.117</v>
       </c>
       <c r="T19" t="n">
-        <v>0.858</v>
+        <v>0.8103</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7433</v>
+        <v>-0.6933</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2393</v>
+        <v>0.2634</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9936</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3342</v>
+        <v>1.4053</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7117</v>
+        <v>0.6185</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6061</v>
+        <v>1.5967</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1623</v>
+        <v>-0.1539</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7683</v>
+        <v>1.7506</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3923</v>
+        <v>0.3416</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.9347</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3101</v>
+        <v>1.2762</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2138</v>
+        <v>1.2551</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7556</v>
+        <v>0.7808</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4583</v>
+        <v>0.4744</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1865</v>
+        <v>-0.1628</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3195</v>
+        <v>0.277</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5059</v>
+        <v>-0.4398</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,64 +2143,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7067</v>
+        <v>0.6054</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3822</v>
+        <v>-2.6192</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0889</v>
+        <v>3.2246</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1829</v>
+        <v>2.1191</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6005</v>
+        <v>2.5281</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4176</v>
+        <v>-0.409</v>
       </c>
       <c r="J21" t="n">
-        <v>0.484</v>
+        <v>0.3794</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1683</v>
+        <v>2.0704</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.6843</v>
+        <v>-1.691</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6989</v>
+        <v>1.7397</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4322</v>
+        <v>0.4577</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2667</v>
+        <v>1.282</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="R21" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4107</v>
+        <v>-0.408</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0352</v>
+        <v>-0.0211</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.446</v>
+        <v>-0.3869</v>
       </c>
       <c r="V21" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="W21" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2226,64 +2226,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.582</v>
+        <v>-0.6798</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5163</v>
+        <v>-3.7716</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9344</v>
+        <v>3.0917</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9481</v>
+        <v>2.9424</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8297</v>
+        <v>1.8267</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1183</v>
+        <v>1.1156</v>
       </c>
       <c r="J22" t="n">
-        <v>1.658</v>
+        <v>1.6071</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.8799</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7543</v>
+        <v>0.7272</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2901</v>
+        <v>1.3352</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9261</v>
+        <v>0.9468</v>
       </c>
       <c r="O22" t="n">
-        <v>0.364</v>
+        <v>0.3885</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.1309</v>
+        <v>-4.2115</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.7374</v>
+        <v>-5.8493</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4812</v>
+        <v>-0.4748</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.519</v>
+        <v>-0.5935</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0378</v>
+        <v>0.1187</v>
       </c>
       <c r="V22" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W22" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2309,40 +2309,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.66</v>
+        <v>-1.6414</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2197</v>
+        <v>-1.2832</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4403</v>
+        <v>-0.3582</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4374</v>
+        <v>-1.4249</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6291</v>
+        <v>-0.6372</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8083</v>
+        <v>-0.7877</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4987</v>
+        <v>-1.5197</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7644</v>
+        <v>-0.7852</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7343</v>
+        <v>-0.7345</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0613</v>
+        <v>0.0949</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1352</v>
+        <v>0.1481</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0532</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0717</v>
+        <v>-0.0822</v>
       </c>
       <c r="T23" t="n">
-        <v>0.279</v>
+        <v>0.2366</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3508</v>
+        <v>-0.3188</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7379</v>
+        <v>-1.7058</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8346</v>
+        <v>-1.9372</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.2313</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9455</v>
+        <v>-0.9142</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.4782</v>
+        <v>-2.45</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5327</v>
+        <v>1.5358</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4394</v>
+        <v>-0.4635</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2548</v>
+        <v>-2.2571</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8155</v>
+        <v>1.7935</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5061</v>
+        <v>-0.4507</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2234</v>
+        <v>-0.193</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2828</v>
+        <v>-0.2577</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6415</v>
+        <v>-0.6574</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2478</v>
+        <v>-0.3038</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3938</v>
+        <v>-0.3536</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.0307</v>
+        <v>17.9847</v>
       </c>
       <c r="E25" t="n">
-        <v>2.013399999999999</v>
+        <v>0.3195000000000008</v>
       </c>
       <c r="F25" t="n">
-        <v>16.0174</v>
+        <v>17.6651</v>
       </c>
       <c r="G25" t="n">
-        <v>16.5658</v>
+        <v>16.3558</v>
       </c>
       <c r="H25" t="n">
-        <v>8.481200000000001</v>
+        <v>8.2789</v>
       </c>
       <c r="I25" t="n">
-        <v>8.084399999999999</v>
+        <v>8.0769</v>
       </c>
       <c r="J25" t="n">
-        <v>8.176600000000001</v>
+        <v>7.4876</v>
       </c>
       <c r="K25" t="n">
-        <v>5.012</v>
+        <v>4.532300000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>3.1647</v>
+        <v>2.9552</v>
       </c>
       <c r="M25" t="n">
-        <v>8.389200000000001</v>
+        <v>8.868400000000003</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4694</v>
+        <v>3.7468</v>
       </c>
       <c r="O25" t="n">
-        <v>4.9198</v>
+        <v>5.121799999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>2.295100000000001</v>
+        <v>2.339699999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.6223</v>
+        <v>-12.8686</v>
       </c>
       <c r="R25" t="n">
-        <v>14.9175</v>
+        <v>15.2083</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0693</v>
+        <v>-0.9743999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2256</v>
+        <v>0.6384000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.2951</v>
+        <v>-1.6126</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2392000000000002</v>
+        <v>0.2634000000000003</v>
       </c>
       <c r="W25" t="n">
-        <v>5.2332</v>
+        <v>5.0623</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.9941</v>
+        <v>-4.7989</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105352_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105352_W2.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.807</v>
+        <v>4.8065</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8685</v>
+        <v>2.9873</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9385</v>
+        <v>1.8192</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8392</v>
+        <v>1.874</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2131</v>
+        <v>2.2373</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3739</v>
+        <v>-0.3632</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4072</v>
+        <v>2.4335</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1144</v>
+        <v>2.1392</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2928</v>
+        <v>0.2943</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.5595</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0987</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6667</v>
+        <v>-0.6576</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1783</v>
+        <v>1.1413</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1988</v>
+        <v>1.269</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0204</v>
+        <v>-0.1277</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2574</v>
+        <v>2.2553</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="X2" t="n">
-        <v>1.591</v>
+        <v>1.5781</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4745</v>
+        <v>2.4652</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8004</v>
+        <v>1.8392</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6741</v>
+        <v>0.626</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5471</v>
+        <v>1.5494</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6188</v>
+        <v>-0.626</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1659</v>
+        <v>2.1754</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2894</v>
+        <v>1.2875</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7579</v>
+        <v>-0.766</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0473</v>
+        <v>2.0535</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2577</v>
+        <v>0.2619</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1391</v>
+        <v>0.14</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1186</v>
+        <v>0.1219</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5877</v>
+        <v>0.5951</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5109</v>
+        <v>0.5517</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0767</v>
+        <v>0.0434</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,64 +736,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5357</v>
+        <v>0.5507</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2826</v>
+        <v>-0.2322</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8184</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.7481</v>
+        <v>-2.7745</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2816</v>
+        <v>-1.2959</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4665</v>
+        <v>-1.4786</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.8186</v>
+        <v>-1.8382</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2764</v>
+        <v>-0.279</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5422</v>
+        <v>-1.5592</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9295</v>
+        <v>-0.9364</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0051</v>
+        <v>-1.0169</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0756</v>
+        <v>0.0805</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5819</v>
+        <v>0.629</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4718</v>
+        <v>0.5343</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1101</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1147</v>
+        <v>0.0964</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2879</v>
+        <v>2.3494</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1732</v>
+        <v>-2.253</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8628</v>
+        <v>0.8625</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0498</v>
+        <v>-0.0504</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9126</v>
+        <v>0.9129</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1225</v>
+        <v>1.116</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0038</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1274</v>
+        <v>1.1198</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2596</v>
+        <v>-0.2534</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0449</v>
+        <v>-0.0465</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2148</v>
+        <v>-0.2069</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4442</v>
+        <v>0.449</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8673</v>
+        <v>0.9296</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4231</v>
+        <v>-0.4806</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.6603</v>
+        <v>-2.6793</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,64 +902,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2007</v>
+        <v>-0.2119</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9059</v>
+        <v>-0.8554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7052</v>
+        <v>0.6435</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8272</v>
+        <v>-1.8482</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9526</v>
+        <v>-0.9629</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8746</v>
+        <v>-0.8854</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.049</v>
+        <v>-1.0729</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0783</v>
+        <v>-1.0889</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0293</v>
+        <v>0.016</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7782</v>
+        <v>-0.7753</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1256</v>
+        <v>0.126</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9039</v>
+        <v>-0.9014</v>
       </c>
       <c r="P6" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1239</v>
+        <v>1.1216</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0443</v>
+        <v>1.0952</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0796</v>
+        <v>0.0264</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2686</v>
+        <v>0.2827</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2686</v>
+        <v>0.2827</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4684</v>
+        <v>-2.4996</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5411</v>
+        <v>-3.5309</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0727</v>
+        <v>1.0313</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3437</v>
+        <v>-3.3788</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6278</v>
+        <v>-0.6353</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.7159</v>
+        <v>-2.7435</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.1078</v>
+        <v>-3.1415</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0498</v>
+        <v>0.0504</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.1576</v>
+        <v>-3.1919</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2359</v>
+        <v>-0.2372</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6776</v>
+        <v>-0.6857</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4417</v>
+        <v>0.4484</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1602</v>
+        <v>-0.1399</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4333</v>
+        <v>-0.3894</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2731</v>
+        <v>0.2495</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,67 +1068,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0111</v>
+        <v>-3.0085</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4235</v>
+        <v>-2.3637</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5876</v>
+        <v>-0.6448</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7255</v>
+        <v>-0.7398</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6621</v>
+        <v>-1.6803</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9365</v>
+        <v>0.9405</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3133</v>
+        <v>-0.3324</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6261</v>
+        <v>-1.6431</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3128</v>
+        <v>1.3107</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4122</v>
+        <v>-0.4074</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0359</v>
+        <v>-0.0372</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3763</v>
+        <v>-0.3702</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8718</v>
+        <v>-1.8566</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5737</v>
+        <v>-2.5528</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6503</v>
+        <v>0.6595</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4635</v>
+        <v>0.5214</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1868</v>
+        <v>0.1381</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1405</v>
+        <v>-3.1255</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4827</v>
+        <v>-3.4142</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3422</v>
+        <v>0.2887</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3556</v>
+        <v>-0.3642</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0301</v>
+        <v>-0.0308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3255</v>
+        <v>-0.3335</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5139</v>
+        <v>-0.5294</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0058</v>
+        <v>0.0065</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5359</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1583</v>
+        <v>0.1652</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0359</v>
+        <v>-0.0372</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1942</v>
+        <v>0.2024</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.8077</v>
+        <v>-2.7849</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7436</v>
+        <v>-3.7131</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9526</v>
+        <v>0.954</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6404</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3121</v>
+        <v>0.2669</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9298</v>
+        <v>-0.9304</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3315</v>
+        <v>-3.3511</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1614</v>
+        <v>-2.1081</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1701</v>
+        <v>-1.243</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4243</v>
+        <v>-2.4521</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4092</v>
+        <v>-2.436</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0151</v>
+        <v>-0.0161</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6236</v>
+        <v>-1.6535</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5431</v>
+        <v>-1.5591</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0805</v>
+        <v>-0.0944</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8007</v>
+        <v>-0.7986</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8661</v>
+        <v>-0.8769</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0654</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7019</v>
+        <v>-0.6962</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.603</v>
+        <v>-0.5974</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.198</v>
+        <v>-0.134</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.405</v>
+        <v>-0.4634</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3978</v>
+        <v>0.3945</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6664</v>
+        <v>-0.6772</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8831</v>
+        <v>-3.8891</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6661</v>
+        <v>-2.6169</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2171</v>
+        <v>-1.2723</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8899</v>
+        <v>-2.9182</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2926</v>
+        <v>-0.2966</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5973</v>
+        <v>-2.6216</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1629</v>
+        <v>-1.1813</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8966</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0595</v>
+        <v>-2.0881</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.727</v>
+        <v>-1.7369</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1891</v>
+        <v>-1.2034</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5335</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7298</v>
+        <v>-0.7178</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0698</v>
+        <v>-0.022</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.66</v>
+        <v>-0.6957</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2634</v>
+        <v>-0.2532</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2634</v>
+        <v>-0.2532</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,64 +1400,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1794</v>
+        <v>-7.2058</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4567</v>
+        <v>-6.3805</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7227</v>
+        <v>-0.8253</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.2908</v>
+        <v>-6.347</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.5676</v>
+        <v>-2.5964</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.7232</v>
+        <v>-3.7506</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.0985</v>
+        <v>-4.1455</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5265</v>
+        <v>-1.5423</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5719</v>
+        <v>-2.6032</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1924</v>
+        <v>-2.2015</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0411</v>
+        <v>-1.0541</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1513</v>
+        <v>-1.1474</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8718</v>
+        <v>-1.8566</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.5096</v>
+        <v>-3.4811</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3495</v>
+        <v>-0.3566</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1814</v>
+        <v>-0.1083</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1682</v>
+        <v>-0.2483</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3327</v>
+        <v>1.3544</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3327</v>
+        <v>1.3544</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.2828</v>
+        <v>-15.3727</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.9632</v>
+        <v>-14.326</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3195999999999998</v>
+        <v>-1.046900000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-16.356</v>
+        <v>-16.5369</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.2791</v>
+        <v>-8.3733</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.077</v>
+        <v>-8.1637</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.868500000000001</v>
+        <v>-9.057700000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.7466</v>
+        <v>-3.7793</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.1218</v>
+        <v>-5.2784</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.487500000000001</v>
+        <v>-7.479099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.5323</v>
+        <v>-4.5938</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.9553</v>
+        <v>-2.8855</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.2083</v>
+        <v>-15.0847</v>
       </c>
       <c r="R13" t="n">
-        <v>12.8685</v>
+        <v>12.764</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6764</v>
+        <v>3.737799999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>4.3145</v>
+        <v>4.9345</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6383</v>
+        <v>-1.1967</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2633000000000001</v>
+        <v>-0.2530999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>4.7989</v>
+        <v>4.8817</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.0623</v>
+        <v>-5.134800000000001</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.062</v>
+        <v>5.1018</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4323</v>
+        <v>2.5434</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6297</v>
+        <v>2.5584</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1364</v>
+        <v>3.1779</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7655</v>
+        <v>2.7961</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3709</v>
+        <v>0.3818</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3614</v>
+        <v>2.387</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1418</v>
+        <v>2.1663</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2196</v>
+        <v>0.2208</v>
       </c>
       <c r="M14" t="n">
-        <v>0.775</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6237</v>
+        <v>0.6298</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1513</v>
+        <v>0.161</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3397</v>
+        <v>2.3207</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3397</v>
+        <v>2.3207</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1128</v>
+        <v>0.1096</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4635</v>
+        <v>0.5214</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3507</v>
+        <v>-0.4118</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5269</v>
+        <v>-0.5064</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3926</v>
+        <v>-0.365</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0672</v>
+        <v>4.0651</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9968</v>
+        <v>4.0645</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0704</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1897</v>
+        <v>3.2267</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7056</v>
+        <v>1.725</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4841</v>
+        <v>1.5017</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7378</v>
+        <v>2.7624</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5665</v>
+        <v>1.585</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1713</v>
+        <v>1.1774</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4519</v>
+        <v>0.4643</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1391</v>
+        <v>0.14</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3128</v>
+        <v>0.3243</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1756</v>
+        <v>0.1422</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3372</v>
+        <v>-0.3055</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5128</v>
+        <v>0.4477</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5962</v>
+        <v>1.6076</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3139</v>
+        <v>3.3032</v>
       </c>
       <c r="E16" t="n">
-        <v>0.663</v>
+        <v>0.7144</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6509</v>
+        <v>2.5887</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5623</v>
+        <v>3.5933</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7751</v>
+        <v>1.795</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7872</v>
+        <v>1.7983</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5322</v>
+        <v>1.54</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3175</v>
+        <v>1.3331</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2148</v>
+        <v>0.2069</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0301</v>
+        <v>2.0533</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4577</v>
+        <v>0.4619</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5724</v>
+        <v>1.5914</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4179</v>
+        <v>0.3871</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3007</v>
+        <v>0.3348</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1173</v>
+        <v>0.0523</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6664</v>
+        <v>-0.6772</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6664</v>
+        <v>-0.6772</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.18</v>
+        <v>3.1786</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0303</v>
+        <v>1.1037</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1498</v>
+        <v>2.075</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9879</v>
+        <v>1.0104</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5472</v>
+        <v>1.5646</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5593</v>
+        <v>-0.5541</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7924</v>
+        <v>0.8015</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4171</v>
+        <v>1.4339</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6247</v>
+        <v>-0.6324</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1955</v>
+        <v>0.209</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1301</v>
+        <v>0.1307</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0654</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3203</v>
+        <v>0.3116</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2379</v>
+        <v>0.3022</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0825</v>
+        <v>0.0094</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1894,64 +1894,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8867</v>
+        <v>2.8899</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3972</v>
+        <v>0.4627</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4895</v>
+        <v>2.4272</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4535</v>
+        <v>1.4529</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0267</v>
+        <v>-1.0375</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4802</v>
+        <v>2.4904</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9174</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9952</v>
+        <v>-1.0049</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9302</v>
+        <v>1.9223</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5355</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0314</v>
+        <v>-0.0326</v>
       </c>
       <c r="O18" t="n">
-        <v>0.55</v>
+        <v>0.5681</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3328</v>
+        <v>-0.3309</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.432</v>
+        <v>-0.366</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0992</v>
+        <v>0.0351</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4912</v>
+        <v>1.4633</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7926</v>
+        <v>0.8376</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6986</v>
+        <v>0.6256</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2931</v>
+        <v>-0.2984</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3985</v>
+        <v>0.403</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6915</v>
+        <v>-0.7014</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2161</v>
+        <v>-1.2385</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1113</v>
+        <v>0.1137</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3274</v>
+        <v>-1.3523</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9231</v>
+        <v>0.9402</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2872</v>
+        <v>0.2893</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6359</v>
+        <v>0.6508</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S19" t="n">
-        <v>0.117</v>
+        <v>0.116</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8103</v>
+        <v>0.8631</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6933</v>
+        <v>-0.7471</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2634</v>
+        <v>0.2532</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.9599</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4053</v>
+        <v>1.3663</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6185</v>
+        <v>0.6493</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.717</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5967</v>
+        <v>1.6057</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1539</v>
+        <v>-0.1558</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7506</v>
+        <v>1.7615</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3416</v>
+        <v>0.3297</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9347</v>
+        <v>-0.9442</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2762</v>
+        <v>1.2739</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2551</v>
+        <v>1.276</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7808</v>
+        <v>0.7884</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4744</v>
+        <v>0.4876</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1628</v>
+        <v>-0.1867</v>
       </c>
       <c r="T20" t="n">
-        <v>0.277</v>
+        <v>0.3196</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4398</v>
+        <v>-0.5063</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,64 +2143,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6054</v>
+        <v>0.6446</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6192</v>
+        <v>-2.5316</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2246</v>
+        <v>3.1762</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1191</v>
+        <v>2.1479</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5281</v>
+        <v>2.5572</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.409</v>
+        <v>-0.4093</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3794</v>
+        <v>0.382</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0704</v>
+        <v>2.0953</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.691</v>
+        <v>-1.7133</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7397</v>
+        <v>1.7658</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4577</v>
+        <v>0.4619</v>
       </c>
       <c r="O21" t="n">
-        <v>1.282</v>
+        <v>1.3039</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6378</v>
+        <v>-1.6245</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.5096</v>
+        <v>-3.4811</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.408</v>
+        <v>-0.4146</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0211</v>
+        <v>0.0316</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3869</v>
+        <v>-0.4462</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2226,64 +2226,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6798</v>
+        <v>-0.6178</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7716</v>
+        <v>-3.6473</v>
       </c>
       <c r="F22" t="n">
-        <v>3.0917</v>
+        <v>3.0295</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9424</v>
+        <v>2.9732</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8267</v>
+        <v>1.8464</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1156</v>
+        <v>1.1268</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6071</v>
+        <v>1.612</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8799</v>
+        <v>0.89</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7272</v>
+        <v>0.722</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3352</v>
+        <v>1.3612</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9468</v>
+        <v>0.9564</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3885</v>
+        <v>0.4048</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.2115</v>
+        <v>-4.1773</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.8493</v>
+        <v>-5.8018</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4748</v>
+        <v>-0.4855</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5935</v>
+        <v>-0.5293</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1187</v>
+        <v>0.0438</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2309,40 +2309,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6414</v>
+        <v>-1.6447</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2832</v>
+        <v>-1.2571</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3582</v>
+        <v>-0.3876</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4249</v>
+        <v>-1.4302</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6372</v>
+        <v>-0.6438</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7877</v>
+        <v>-0.7864</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5197</v>
+        <v>-1.5359</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7852</v>
+        <v>-0.7931</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7345</v>
+        <v>-0.7428</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0949</v>
+        <v>0.1057</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1481</v>
+        <v>0.1493</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0532</v>
+        <v>-0.0436</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0822</v>
+        <v>-0.0732</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2366</v>
+        <v>0.2788</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3188</v>
+        <v>-0.352</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7058</v>
+        <v>-1.7128</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9372</v>
+        <v>-1.8928</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2313</v>
+        <v>0.18</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9142</v>
+        <v>-0.9225</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.45</v>
+        <v>-2.477</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5358</v>
+        <v>1.5546</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4635</v>
+        <v>-0.4783</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2571</v>
+        <v>-2.2812</v>
       </c>
       <c r="L24" t="n">
-        <v>1.7935</v>
+        <v>1.8028</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4507</v>
+        <v>-0.4441</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.193</v>
+        <v>-0.1959</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2577</v>
+        <v>-0.2483</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6574</v>
+        <v>-0.649</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3038</v>
+        <v>-0.2541</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3536</v>
+        <v>-0.3949</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>17.9847</v>
+        <v>18.0375</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3195000000000008</v>
+        <v>1.0468</v>
       </c>
       <c r="F25" t="n">
-        <v>17.6651</v>
+        <v>16.9906</v>
       </c>
       <c r="G25" t="n">
-        <v>16.3558</v>
+        <v>16.5369</v>
       </c>
       <c r="H25" t="n">
-        <v>8.2789</v>
+        <v>8.373199999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>8.0769</v>
+        <v>8.163900000000002</v>
       </c>
       <c r="J25" t="n">
-        <v>7.4876</v>
+        <v>7.479300000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.532300000000001</v>
+        <v>4.5939</v>
       </c>
       <c r="L25" t="n">
-        <v>2.9552</v>
+        <v>2.8853</v>
       </c>
       <c r="M25" t="n">
-        <v>8.868400000000003</v>
+        <v>9.057700000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7468</v>
+        <v>3.779199999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>5.121799999999999</v>
+        <v>5.2783</v>
       </c>
       <c r="P25" t="n">
-        <v>2.339699999999999</v>
+        <v>2.3207</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.8686</v>
+        <v>-12.7641</v>
       </c>
       <c r="R25" t="n">
-        <v>15.2083</v>
+        <v>15.0848</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9743999999999999</v>
+        <v>-1.0734</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6384000000000001</v>
+        <v>1.1966</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6126</v>
+        <v>-2.27</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2634000000000003</v>
+        <v>0.2533000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>5.0623</v>
+        <v>5.1349</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.7989</v>
+        <v>-4.881600000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>
